--- a/base/pacotes/arthen-arboris/executivo-arthen-arboris.xlsx
+++ b/base/pacotes/arthen-arboris/executivo-arthen-arboris.xlsx
@@ -231,6 +231,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,9 +244,6 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 2026-04-13T17:11:13 | AC=12473 m² | UR=98 | baseado em 5 projetos similares</t>
+          <t>Gerado em 2026-04-13T22:57:48 | AC=12473 m² | UR=98 | baseado em 5 projetos similares</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         <v>0.07692813615224015</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>0.06692310587986283</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>0.05200871364274728</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>0.02092968944902759</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>0.01342325742435531</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>0.04274784843416538</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>0.0113951622155605</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>0.04599471616298692</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>0.01740471324322299</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1487,29 +1487,29 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Equipamentos de ar condicionado em áreas comuns</t>
+          <t>Unidade Condensadora 36.000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>Unid.</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>318647</v>
+        <v>4500</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>318647</v>
+        <v>15750</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -1519,29 +1519,29 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Sistema de climatização e exaustão mecânica</t>
+          <t>Unidade Evaporadora Hi wall, 36000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>Unid.</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>313577.59</v>
+        <v>4252.53</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>313577.59</v>
+        <v>14883.855</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra</t>
+          <t>Unidade Condensadora 24.000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>190067.16456</v>
+        <v>3901.59</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>190067.16456</v>
+        <v>7803.18</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Unidade Condensadora 36.000 BTU/h, LG ou similar</t>
+          <t>Unidade Evaporadora Hi wall, 24000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>4500</v>
+        <v>3311.42</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>15750</v>
+        <v>6622.84</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Unidade Evaporadora Hi wall, 36000 BTU/h, LG ou similar</t>
+          <t>Unidade Condensadora 12.000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>4252.53</v>
+        <v>1918.08</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>14883.855</v>
+        <v>4795.2</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Unidade Condensadora 24.000 BTU/h, LG ou similar</t>
+          <t>Unidade Evaporadora Hi wall, 12000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>3901.59</v>
+        <v>1792.01</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>7803.18</v>
+        <v>4480.025</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Unidade Evaporadora Hi wall, 24000 BTU/h, LG ou similar</t>
+          <t>Unidade Evaporadora Hi wall, 9000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -1691,10 +1691,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>3311.42</v>
+        <v>1625</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>6622.84</v>
+        <v>3250</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -1711,22 +1711,22 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Unidade Condensadora Multisplit 36.000 BTU/h, LG ou similar</t>
+          <t>Rede frigorígena para Split de 9000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø1/4’’ + Isolamento Linha de Sucção: Tubo de cobre Ø3/8’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>Unid.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>1</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>6558.35</v>
+        <v>39.87733333333333</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>6558.35</v>
+        <v>3128.775573333333</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Unidade Condensadora 12.000 BTU/h, LG ou similar</t>
+          <t>Unidade Condensadora 9.000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>1918.08</v>
+        <v>1491.6</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>4795.2</v>
+        <v>2983.2</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Unidade Evaporadora Hi wall, 12000 BTU/h, LG ou similar</t>
+          <t>Unidade Condensadora 18.000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1792.01</v>
+        <v>2769.58</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>4480.025</v>
+        <v>2769.58</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Unidade Evaporadora Hi wall, 9000 BTU/h, LG ou similar</t>
+          <t>Unidade Evaporadora Hi wall, 18000 BTU/h, LG ou similar</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -1816,13 +1816,13 @@
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>1625</v>
+        <v>2356.92</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>3250</v>
+        <v>2356.92</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Rede frigorígena para Split de 9000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø1/4’’ + Isolamento Linha de Sucção: Tubo de cobre Ø3/8’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
+          <t>Rede frigorígena para Split de 18000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø1/4’’ + Isolamento Linha de Sucção: Tubo de cobre Ø1/2’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>78.45999999999999</v>
+        <v>52.345</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>39.87733333333333</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>3128.775573333333</v>
+        <v>2087.379013333333</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Unidade Condensadora 9.000 BTU/h, LG ou similar</t>
+          <t>Rede frigorígena para Split de 24000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø1/4’’ + Isolamento Linha de Sucção: Tubo de cobre Ø5/8’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>Unid.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>2</v>
+        <v>42.23</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>1491.6</v>
+        <v>39.87733333333333</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>2983.2</v>
+        <v>1684.019786666667</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
@@ -1903,22 +1903,22 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Unidade Condensadora 18.000 BTU/h, LG ou similar</t>
+          <t>Rede frigorígena para Split de 36000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø3/8’’ + Isolamento Linha de Sucção: Tubo de cobre Ø5/8’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>Unid.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>1</v>
+        <v>43.245</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>2769.58</v>
+        <v>39.87733333333333</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>2769.58</v>
+        <v>1724.49528</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Unidade Evaporadora Hi wall, 18000 BTU/h, LG ou similar</t>
+          <t>Rede frigorígena para Split de 12000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø1/4’’ + Isolamento Linha de Sucção: Tubo de cobre Ø3/8’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>Unid.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D19" s="25" t="n">
-        <v>1</v>
+        <v>28.75</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>2356.92</v>
+        <v>39.87733333333333</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>2356.92</v>
+        <v>1146.473333333333</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
@@ -1967,155 +1967,27 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Rede frigorígena para Split de 18000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø1/4’’ + Isolamento Linha de Sucção: Tubo de cobre Ø1/2’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
+          <t>Caixa Polar</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Unid.</t>
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>52.345</v>
+        <v>10</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>39.87733333333333</v>
+        <v>22.96</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>2087.379013333333</v>
+        <v>229.6</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>fonseca-empreendimentos-estoril</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>Rede frigorígena para Split de 24000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø1/4’’ + Isolamento Linha de Sucção: Tubo de cobre Ø5/8’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="n">
-        <v>42.23</v>
-      </c>
-      <c r="E21" s="26" t="n">
-        <v>39.87733333333333</v>
-      </c>
-      <c r="F21" s="27" t="n">
-        <v>1684.019786666667</v>
-      </c>
-      <c r="G21" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>fonseca-empreendimentos-estoril</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>Rede frigorígena para Split de 36000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø3/8’’ + Isolamento Linha de Sucção: Tubo de cobre Ø5/8’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="n">
-        <v>43.245</v>
-      </c>
-      <c r="E22" s="26" t="n">
-        <v>39.87733333333333</v>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>1724.49528</v>
-      </c>
-      <c r="G22" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>fonseca-empreendimentos-estoril</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>Rede frigorígena para Split de 12000Btu/h contendo: Linha de Líquido: Tubo de cobre Ø1/4’’ + Isolamento Linha de Sucção: Tubo de cobre Ø3/8’’ + Isolamento 1 x Cabo PP#4x1,5mm² Eletroduto Flexível de PVC 25mm</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="n">
-        <v>28.75</v>
-      </c>
-      <c r="E23" s="26" t="n">
-        <v>39.87733333333333</v>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>1146.473333333333</v>
-      </c>
-      <c r="G23" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>fonseca-empreendimentos-estoril</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>Caixa Polar</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>Unid.</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" s="26" t="n">
-        <v>22.96</v>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>229.6</v>
-      </c>
-      <c r="G24" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
@@ -2904,7 +2776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3171,22 +3043,22 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Pintura de Tubulações - (MAT + MDO)</t>
+          <t>Pintura com tinta hidrofugante, aplicação manual, 2 demãos, em concreto aparente</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>1</v>
+        <v>423.075</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>10000</v>
+        <v>18.6979</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>10000</v>
+        <v>7910.6140425</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -3203,59 +3075,27 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Pintura com tinta hidrofugante, aplicação manual, 2 demãos, em concreto aparente</t>
+          <t>Pintura Portas de Madeira da Entrada</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>423.075</v>
+        <v>134</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>18.6979</v>
+        <v>22.8596</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>7910.6140425</v>
+        <v>3063.1864</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>somauma-virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Pintura Portas de Madeira da Entrada</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>134</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>22.8596</v>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>3063.1864</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>somauma-virginia</t>
         </is>
@@ -3928,22 +3768,22 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Locação de Balancim para Abertura de Janelas do Bloco B</t>
+          <t>Guarda-corpo em alumínio e vidro h=110cm</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D23" s="25" t="n">
-        <v>1</v>
+        <v>6.974</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>18000</v>
+        <v>1900.8</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>18000</v>
+        <v>13256.1792</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
@@ -3960,22 +3800,22 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Guarda-corpo em alumínio e vidro h=110cm</t>
+          <t>Janela com caixilho folha superior maximar e bandeira inferior fixa em vidro transparente. - 1,1 x 1,75 m</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D24" s="25" t="n">
-        <v>6.974</v>
+        <v>9</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>1900.8</v>
+        <v>1409.1</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>13256.1792</v>
+        <v>12681.9</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>1</v>
@@ -3992,7 +3832,7 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Janela com caixilho folha superior maximar e bandeira inferior fixa em vidro transparente. - 1,1 x 1,75 m</t>
+          <t>Porta de madeira de abrir 92x210cm, fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -4001,13 +3841,13 @@
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>1409.1</v>
+        <v>1027.598</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>12681.9</v>
+        <v>10275.98</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
@@ -4024,7 +3864,7 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>Porta de madeira de abrir 92x210cm, fixação com espuma expansiva</t>
+          <t>Mão de obra para instalação de esquadrias de ferro</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -4033,13 +3873,13 @@
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>1027.598</v>
+        <v>141.613</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>10275.98</v>
+        <v>6089.359</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>1</v>
@@ -4056,22 +3896,22 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Pintura sobre Esquadrias de Ferro - (MAT + MDO)</t>
+          <t>Execução de contramarco de porta corta-fogo</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>1</v>
+        <v>220.3</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>10000</v>
+        <v>17.3444</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>10000</v>
+        <v>3820.97132</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>1</v>
@@ -4088,7 +3928,7 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra para instalação de esquadrias de ferro</t>
+          <t>S.A.L. - Placa "Porta corta fogo - Manter fechada"</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -4097,20 +3937,20 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>141.613</v>
+        <v>49.1</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>6089.359</v>
+        <v>3731.6</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -4120,22 +3960,22 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Execução de contramarco de porta corta-fogo</t>
+          <t>Porta de madeira dupla de abrir 140x210cm, fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>220.3</v>
+        <v>3</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>17.3444</v>
+        <v>1177.7116</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>3820.97132</v>
+        <v>3533.1348</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
@@ -4152,7 +3992,7 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>S.A.L. - Placa "Porta corta fogo - Manter fechada"</t>
+          <t>Janela com caixilho 1 folha de abrir e bandeira superior pivotante/maximar, todas em vidro translúcido. - 0,87 x 2,45 m</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -4161,20 +4001,20 @@
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>49.1</v>
+        <v>1560.258</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>3731.6</v>
+        <v>3120.516</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>somauma-virginia</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4024,7 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Porta de madeira dupla de abrir 140x210cm, fixação com espuma expansiva</t>
+          <t>Janela com especificação caixilho 2 folhas de correr em vidro transparente e bandeira superior maximar em vidro translúcido - 1,8 x 1,27 m</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -4193,13 +4033,13 @@
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>1177.7116</v>
+        <v>3022.45776</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>3533.1348</v>
+        <v>3022.45776</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>1</v>
@@ -4216,7 +4056,7 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Janela com caixilho 1 folha de abrir e bandeira superior pivotante/maximar, todas em vidro translúcido. - 0,87 x 2,45 m</t>
+          <t>Porta de madeira dupla de abrir 120x210cm, fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -4225,13 +4065,13 @@
         </is>
       </c>
       <c r="D32" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1560.258</v>
+        <v>1159.7116</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>3120.516</v>
+        <v>1159.7116</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>1</v>
@@ -4248,7 +4088,7 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Janela com especificação caixilho 2 folhas de correr em vidro transparente e bandeira superior maximar em vidro translúcido - 1,8 x 1,27 m</t>
+          <t>Janela com caixilho 5 folhas. inferior fixa e 4 superiores pivotantes/maximar, todas em vidro translúcido. - 0,99 x 1,27 m</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -4260,10 +4100,10 @@
         <v>1</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>3022.45776</v>
+        <v>971.4738</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>3022.45776</v>
+        <v>971.4738</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>1</v>
@@ -4280,7 +4120,7 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>Porta de madeira dupla de abrir 120x210cm, fixação com espuma expansiva</t>
+          <t>Condulete de alumínio Tipo ''TB'', à prova de tempo, com tampa cega, junta de vedação em E.V.A, pintura epoxi cor cinza, para eletroduto rígido de aço DN25mm, rosca Ø1'' BSP</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -4289,20 +4129,20 @@
         </is>
       </c>
       <c r="D34" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>1159.7116</v>
+        <v>21.54</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>1159.7116</v>
+        <v>43.08</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4621,29 +4461,29 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Cavalete e Registro de Água</t>
+          <t>Válvula reta com registro de Fecho Rápido 1/2'' BSP</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>14500</v>
+        <v>28.28</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>14500</v>
+        <v>6391.280000000001</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4493,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Válvula reta com registro de Fecho Rápido 1/2'' BSP</t>
+          <t>Cuba Pia Cozinha - Lazer</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -4662,13 +4502,13 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>226</v>
+        <v>3</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>28.28</v>
+        <v>1981.262</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>6391.280000000001</v>
+        <v>5943.786</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
@@ -4685,7 +4525,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Cuba Pia Cozinha - Lazer</t>
+          <t>Registro Globo Angular 2.1/2"</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -4694,13 +4534,13 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1981.262</v>
+        <v>149.9</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>5943.786</v>
+        <v>5246.5</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
@@ -4717,7 +4557,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Registro Globo Angular 2.1/2"</t>
+          <t>Registro de Gaveta Industrial, Bronze - 2.1/2"</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -4726,13 +4566,13 @@
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>149.9</v>
+        <v>433.48</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>5246.5</v>
+        <v>5201.76</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
@@ -4749,7 +4589,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Registro de Gaveta Industrial, Bronze - 2.1/2"</t>
+          <t>Lavatório suspenso \ Detalhe: Cuba viggo 54cm branca</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -4758,20 +4598,20 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>433.48</v>
+        <v>450</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>5201.76</v>
+        <v>4050</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4621,7 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Lavatório suspenso \ Detalhe: Cuba viggo 54cm branca</t>
+          <t>Banheiro - Bacia Sanitária PNE</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -4790,20 +4630,20 @@
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>450</v>
+        <v>937.3399999999999</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>4050</v>
+        <v>4218.03</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby</t>
+          <t>cln-porto-ruby, fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4653,7 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Banheiro - Bacia Sanitária PNE</t>
+          <t>Torneira Lavatório mesa</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -4822,13 +4662,13 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>937.3399999999999</v>
+        <v>235</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>4218.03</v>
+        <v>3172.5</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>2</v>
@@ -4845,7 +4685,7 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Torneira Lavatório mesa</t>
+          <t>SHP - Bacia de contenção - 375 Litros - Abaixo do Tanque</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -4854,20 +4694,20 @@
         </is>
       </c>
       <c r="D19" s="25" t="n">
-        <v>13.5</v>
+        <v>2</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>235</v>
+        <v>1259</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>3172.5</v>
+        <v>2518</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby, fonseca-empreendimentos-estoril</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4717,7 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>SHP - Bacia de contenção - 375 Litros - Abaixo do Tanque</t>
+          <t>GÁS - Registro de fecho rápido com caixa</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -4889,10 +4729,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>1259</v>
+        <v>1098.98</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>2518</v>
+        <v>2197.96</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
@@ -4909,7 +4749,7 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>GÁS - Registro de fecho rápido com caixa</t>
+          <t>Torneira para Lavatório\ Detalhe: Cromado Vercci</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -4918,20 +4758,20 @@
         </is>
       </c>
       <c r="D21" s="25" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>1098.98</v>
+        <v>120</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>2197.96</v>
+        <v>2160</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4781,7 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Torneira para Lavatório\ Detalhe: Cromado Vercci</t>
+          <t>Banheiro - Cuba de Sobrepor - PNE</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -4950,20 +4790,20 @@
         </is>
       </c>
       <c r="D22" s="25" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>120</v>
+        <v>492.8899999999999</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>2160</v>
+        <v>985.7799999999999</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4813,7 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Banheiro - Cuba de Sobrepor - PNE</t>
+          <t>Cozinha - Cuba / Inox</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -4985,17 +4825,17 @@
         <v>2</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>492.8899999999999</v>
+        <v>432.69</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>985.7799999999999</v>
+        <v>865.38</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby, fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -5005,7 +4845,7 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Cozinha - Cuba / Inox</t>
+          <t>Cozinha - Cuba Dupla / Inox</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -5014,20 +4854,20 @@
         </is>
       </c>
       <c r="D24" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>432.69</v>
+        <v>783.2362499999999</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>865.38</v>
+        <v>783.2362499999999</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby, fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby</t>
         </is>
       </c>
     </row>
@@ -5037,7 +4877,7 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Cozinha - Cuba Dupla / Inox</t>
+          <t>Torneira misturador pia cozinha</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -5046,20 +4886,20 @@
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>783.2362499999999</v>
+        <v>250</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>783.2362499999999</v>
+        <v>750</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby</t>
+          <t>cln-porto-ruby, fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -5069,7 +4909,7 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>Torneira misturador pia cozinha</t>
+          <t>Torneira de Jardins</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -5078,13 +4918,13 @@
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>3</v>
+        <v>11.5</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>250</v>
+        <v>48.305</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>750</v>
+        <v>555.5075000000001</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>2</v>
@@ -5101,7 +4941,7 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Torneira de Jardins</t>
+          <t>Acabamento de Registro Pressão</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -5110,13 +4950,13 @@
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>11.5</v>
+        <v>1</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>48.305</v>
+        <v>110</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>555.5075000000001</v>
+        <v>110</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>2</v>
@@ -5133,7 +4973,7 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>Acabamento de Registro Pressão</t>
+          <t>Torneira de jardim inox</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -5142,20 +4982,20 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>110</v>
+        <v>24.61</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>110</v>
+        <v>98.44</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby, fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5005,7 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Torneira de jardim inox</t>
+          <t>Válvula reta com registro de Fecho Rápido 3/4'' BSP</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -5174,20 +5014,20 @@
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>24.61</v>
+        <v>47.4</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>98.44</v>
+        <v>94.8</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5037,7 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>Válvula reta com registro de Fecho Rápido 3/4'' BSP</t>
+          <t>Torneira tanque</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -5206,20 +5046,20 @@
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>94.8</v>
+        <v>52</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5069,7 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Torneira tanque</t>
+          <t>Torneira de bancada para tanque \ Detalhe: Parede inox</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -5250,38 +5090,6 @@
         <v>1</v>
       </c>
       <c r="H31" s="24" t="inlineStr">
-        <is>
-          <t>cln-porto-ruby</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>Torneira de bancada para tanque \ Detalhe: Parede inox</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="26" t="n">
-        <v>52</v>
-      </c>
-      <c r="F32" s="27" t="n">
-        <v>52</v>
-      </c>
-      <c r="G32" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>cln-porto-ruby</t>
         </is>
@@ -5303,7 +5111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5538,91 +5346,27 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Proteção de Pastilhas e Pisos a Serem Restaurados</t>
+          <t>Revestimento interno/externo de parede em pastilha porcelana</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>1</v>
+        <v>24.17</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>15000</v>
+        <v>435.865</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>15000</v>
+        <v>10534.85705</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>somauma-virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Revestimento interno/externo de parede em pastilha porcelana</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>24.17</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>435.865</v>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>10534.85705</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>somauma-virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Ensaio de arrancamento fachada</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>340</v>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>340</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>somauma-virginia</t>
         </is>
@@ -5719,29 +5463,25 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Mobiliário e decoração</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Quadra Poliesportiva</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr"/>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>205.99</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>555000</v>
+        <v>1168.3515625</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>555000</v>
+        <v>240668.738359375</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -5751,29 +5491,25 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Paisagismo</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Espreguiçadeira Calhetas em Corda Pet Cinza</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr"/>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>329756</v>
+        <v>6620</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>329756</v>
+        <v>52960</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -5783,18 +5519,18 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Quadra Poliesportiva</t>
+          <t>Esteira Profissional Adidas T-23 (T-23) - Adidas</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr"/>
       <c r="D7" s="25" t="n">
-        <v>205.99</v>
+        <v>2</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>1168.3515625</v>
+        <v>25172</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>240668.738359375</v>
+        <v>50344</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -5811,18 +5547,18 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Espreguiçadeira Calhetas em Corda Pet Cinza</t>
+          <t>Esteira Profissional Adidas T-23  (T-23) - Adidas</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr"/>
       <c r="D8" s="25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>6620</v>
+        <v>20137.6</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>52960</v>
+        <v>40275.2</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
@@ -5839,29 +5575,25 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Limpeza Final da Obra - Apartamentos</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Cadeira Arco Encosto Estofado</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr"/>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>16.5</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>50400</v>
+        <v>1938.9</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>50400</v>
+        <v>31991.85</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5603,7 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Esteira Profissional Adidas T-23 (T-23) - Adidas</t>
+          <t>Elíptico Adidas X-21</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr"/>
@@ -5879,17 +5611,17 @@
         <v>2</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>25172</v>
+        <v>14490</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>50344</v>
+        <v>28980</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -5899,18 +5631,18 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Espelhos</t>
+          <t>Cadeira Paloma sem braçoNomade Home</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr"/>
       <c r="D11" s="25" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>40288.93390624999</v>
+        <v>1390</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>100722.334765625</v>
+        <v>27800</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -5927,18 +5659,18 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Esteira Profissional Adidas T-23  (T-23) - Adidas</t>
+          <t>Refrigerador Expositor Venax EXPVBL 330 Preto Fosco</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr"/>
       <c r="D12" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>20137.6</v>
+        <v>6890</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>40275.2</v>
+        <v>27560</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
@@ -5955,25 +5687,25 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Playground Dolphin Playground T em Madeira para Quintal com Escorregador</t>
+          <t>Cadeira Com Almofada Em Corda Náutica Área Externa</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr"/>
       <c r="D13" s="25" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>32000</v>
+        <v>811.2</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>32000</v>
+        <v>19468.8</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -5983,25 +5715,25 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Arco Encosto Estofado</t>
+          <t>Cadeira Palermo Scaburi</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr"/>
       <c r="D14" s="25" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1938.9</v>
+        <v>2530</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>31991.85</v>
+        <v>18975</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -6011,29 +5743,25 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Mobiliário de apoio à obra</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Mesa Lateral Deck Externa 50cm x 39cm</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr"/>
       <c r="D15" s="25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>30600</v>
+        <v>2579</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>30600</v>
+        <v>18053</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -6043,18 +5771,18 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Elevador De Acessibilidade Para Piscina Everest Maro Marol</t>
+          <t>Espreguiçadeira de Madeira Tramontina em Jatobá Eco Blindage e Encosto Bege em Fibra</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr"/>
       <c r="D16" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>29650</v>
+        <v>2161.06</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>29650</v>
+        <v>17288.48</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
@@ -6071,25 +5799,25 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Elíptico Adidas X-21</t>
+          <t>Banqueta com Braço Isis Estofada Encosto Detalhe em Madeira Estrutura Madeira Liptus Design Sustentável</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr"/>
       <c r="D17" s="25" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>14490</v>
+        <v>2178</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>28980</v>
+        <v>14157</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -6099,18 +5827,18 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Paloma sem braçoNomade Home</t>
+          <t>Poltrona Nature | Área Externa</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr"/>
       <c r="D18" s="25" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>1390</v>
+        <v>5999</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>27800</v>
+        <v>11998</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
@@ -6127,18 +5855,18 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Refrigerador Expositor Venax EXPVBL 330 Preto Fosco</t>
+          <t>Painel Marcenaria</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr"/>
       <c r="D19" s="25" t="n">
-        <v>4</v>
+        <v>13.92</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>6890</v>
+        <v>850</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>27560</v>
+        <v>11832</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
@@ -6155,29 +5883,25 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Limpeza Final da Obra - Áreas Comuns</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Cortina</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr"/>
       <c r="D20" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>25000</v>
+        <v>2900</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>25000</v>
+        <v>11600</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril, viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -6187,25 +5911,25 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Mesa de Bilhar Versátil 2P Vintage</t>
+          <t>Quadro Decorativo Abstrato Mar, Moldura Preta</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr"/>
       <c r="D21" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>24000</v>
+        <v>5589</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>24000</v>
+        <v>11178</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -6215,18 +5939,18 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Hyper Cross com Smith Vibranium - 60 kg  (VHC-60) - VIBRANIUM</t>
+          <t>Cadeira Soer Fixa 4 Pés Alta Azul</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr"/>
       <c r="D22" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>20720</v>
+        <v>1345.63</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>20720</v>
+        <v>10765.04</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
@@ -6243,25 +5967,25 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Com Almofada Em Corda Náutica Área Externa</t>
+          <t>Futon Sofá Cama Casal Oriental Acquablock Branco Off</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr"/>
       <c r="D23" s="25" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>811.2</v>
+        <v>1790.01</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>19468.8</v>
+        <v>10740.06</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -6271,18 +5995,18 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Palermo Scaburi</t>
+          <t>Lava e Seca Samsung WD11M com Digital Inverter WD11M4473PW Branca 11/7kg - 110V</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr"/>
       <c r="D24" s="25" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>2530</v>
+        <v>3519</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>18975</v>
+        <v>10557</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>1</v>
@@ -6299,25 +6023,25 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Mesa Lateral Deck Externa 50cm x 39cm</t>
+          <t>Mesa Redonda Tampo De Madeira 90cm Para Area Externa/interna</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr"/>
       <c r="D25" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>2579</v>
+        <v>1731</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>18053</v>
+        <v>10386</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -6327,18 +6051,18 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>Espreguiçadeira de Madeira Tramontina em Jatobá Eco Blindage e Encosto Bege em Fibra</t>
+          <t>Acabamentos Especiais</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr"/>
       <c r="D26" s="25" t="n">
-        <v>8</v>
+        <v>21.92</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>2161.06</v>
+        <v>450</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>17288.48</v>
+        <v>9864</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>1</v>
@@ -6355,18 +6079,18 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Sofá Em Corda Náutica Aymara 3 Lugares (03)</t>
+          <t>Conjunto Mesa de Jantar Mobile Tampo Redondo Laqueado com Vidro e 04 Cadeiras Mobile</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr"/>
       <c r="D27" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>15980</v>
+        <v>4774</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>15980</v>
+        <v>9548</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>1</v>
@@ -6383,18 +6107,18 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>Itens de concreto - Bancos</t>
+          <t>Conjunto com Mesa Ripada + 4 Cadeiras de Jardim e Piscina + Ombrelone com Base</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr"/>
       <c r="D28" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>15000</v>
+        <v>4598</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>15000</v>
+        <v>9196</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>1</v>
@@ -6411,18 +6135,18 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Bancada em bloco rustico de granito com acabamento de madeira</t>
+          <t>Poltrona de Madeira Maciça de Eucalipto cor Castanheira com Encosto em Corda Oasis Preto</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr"/>
       <c r="D29" s="25" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>15000</v>
+        <v>769</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>15000</v>
+        <v>8459</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
@@ -6439,25 +6163,25 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>Spinning Profissional Adidas (C-21X) - Adidas</t>
+          <t>Poltrona Em Corda Náutica C/ Almofada Area Externa E Interna - Sarah Móveis</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr"/>
       <c r="D30" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>14350</v>
+        <v>2088</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>14350</v>
+        <v>8352</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -6467,18 +6191,18 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Sofá Fixo Éden Living Modular Curvo Com Ilha e Almofadas Soltas</t>
+          <t>Puffe Boris Boucle Supreme cor Musgo</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr"/>
       <c r="D31" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>14202.88</v>
+        <v>1950</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>14202.88</v>
+        <v>7800</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>1</v>
@@ -6495,18 +6219,18 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Banqueta com Braço Isis Estofada Encosto Detalhe em Madeira Estrutura Madeira Liptus Design Sustentável</t>
+          <t>Cadeira Rafaela Ponta de Mesa Estofada em Madeira Maciça Capuccino Boucle Marfim</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr"/>
       <c r="D32" s="25" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>2178</v>
+        <v>1258</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>14157</v>
+        <v>7548</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>1</v>
@@ -6523,25 +6247,25 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Adutora/Abdutora  (TF27) - Titanium Elite</t>
+          <t>Banqueta Thae - Estrutura em Jequitibá natural com assento em couro Camel.</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr"/>
       <c r="D33" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>13205.65</v>
+        <v>3334</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>13205.65</v>
+        <v>6668</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -6551,25 +6275,25 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Flexora/Extensora  (TF25) - Titanium Elite</t>
+          <t>Quadro Decorativo 1 Tela: Obra Abstrata Moderna e Sofisticada,</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr"/>
       <c r="D34" s="25" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>13205.65</v>
+        <v>697</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>13205.65</v>
+        <v>6621.5</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -6659,36 +6383,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Imprevistos Diversos</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D5" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>947132.0015833681</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>947132.0015833681</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>somauma-virginia</t>
-        </is>
-      </c>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6706,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6834,38 +6534,6 @@
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>somauma-virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Instalações de Fábrica - (Almoxarifado, Baias, etc)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>somauma-virginia</t>
         </is>
@@ -6938,7 +6606,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="n">
+      <c r="A4" s="29" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="18" t="inlineStr">
@@ -6946,19 +6614,19 @@
           <t>viva4-barra4</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>13223.26</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>99</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="31" t="n"/>
+      <c r="F4" s="32" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="29" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="18" t="inlineStr">
@@ -6966,19 +6634,19 @@
           <t>xpcon-porto-cerro</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>13188.75</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="29" t="n">
         <v>86</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="31" t="n"/>
+      <c r="F5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n">
+      <c r="A6" s="29" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="18" t="inlineStr">
@@ -6986,21 +6654,21 @@
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>14491.98</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="29" t="n">
         <v>110</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="31" t="n">
         <v>3378.446360574308</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="32" t="n">
         <v>48960377.08851565</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n">
+      <c r="A7" s="29" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="18" t="inlineStr">
@@ -7008,19 +6676,19 @@
           <t>cln-porto-ruby</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>12972.67</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="29" t="n">
         <v>44</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="31" t="n"/>
+      <c r="F7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="n">
+      <c r="A8" s="29" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="18" t="inlineStr">
@@ -7028,16 +6696,16 @@
           <t>somauma-virginia</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>10108.43</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="29" t="n">
         <v>117</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="31" t="n"/>
+      <c r="F8" s="32" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7427,476 +7095,476 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>Fundação e Supraestrutura</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Quantificação seguindo detalhamentos de projeto e resumo de quantitativo disponibilizado</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>Fundação Rasa</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Escavação e reaterro de Fundação Rasa</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>Fundação Rasa</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Lastro de concreto magro em Fundação Rasa</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Fundação Rasa</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>Rebaixamento de lençol freático para o tempo de fundação</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>Infraestrutura</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>Armação com consideração de aço cortado e dobra em obra com 10% de perda</t>
         </is>
       </c>
-      <c r="C28" s="32" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Infraestrutura</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>Concreto fck de 35 MPa em rasa com 5% de perda</t>
         </is>
       </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>Fabricação de forma de pilares, vigas, lajes, rampas e escadarias em tábua, considerando 2 jogos</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>Armação com consideração de aço cortado e dobra em obra com 10% de perda;</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>Concreto fck de 30 Mpa para estacas, com 30% de perda;</t>
         </is>
       </c>
-      <c r="C32" s="32" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>Concreto fck de 30 Mpa e 40Mpa em fundação rasa e cortina, com 5% de perda;</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>Rebaixamento de lençol freático;</t>
         </is>
       </c>
-      <c r="C34" s="32" t="inlineStr">
+      <c r="C34" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>Armação com aço cortado e dobrado em obra, consideração de 10% de perda;</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B36" s="32" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>Sistema de protensão de vigas;</t>
         </is>
       </c>
-      <c r="C36" s="32" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>Concreto fck de 45 Mpa, incluindo serviço de bombeamento, consideração de 5% de perda;</t>
         </is>
       </c>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>Locação de escoramento de metálico;</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>Mão de obra de supraestrutura.</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>Instalações</t>
         </is>
       </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>Os valores das instalações, preventivas, hidráulicas, elétricas, gás, SPDA e comunicação foram consideradas através de levantamento de itens de listagem de quantidades dos projetos disponibilizados;</t>
         </is>
       </c>
-      <c r="C40" s="32" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>Acabamentos</t>
         </is>
       </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B41" s="28" t="inlineStr">
         <is>
           <t>Consideração dos acabamentos conforme áreas de aplicação do modelo;</t>
         </is>
       </c>
-      <c r="C41" s="32" t="inlineStr">
+      <c r="C41" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>Geral</t>
         </is>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>Estrutura de concreto com alvenaria de vedação.</t>
         </is>
       </c>
-      <c r="C42" s="32" t="inlineStr">
+      <c r="C42" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="inlineStr">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>Lazer</t>
         </is>
       </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B43" s="28" t="inlineStr">
         <is>
           <t>Duas áreas de lazer, com piscina, academia, salão de festa.</t>
         </is>
       </c>
-      <c r="C43" s="32" t="inlineStr">
+      <c r="C43" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>Acabamento</t>
         </is>
       </c>
-      <c r="B44" s="32" t="inlineStr">
+      <c r="B44" s="28" t="inlineStr">
         <is>
           <t>Apartamentos tipo e duplex com piso de porcelanato e vinílico.</t>
         </is>
       </c>
-      <c r="C44" s="32" t="inlineStr">
+      <c r="C44" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="inlineStr">
+      <c r="A45" s="28" t="inlineStr">
         <is>
           <t>Acabamento</t>
         </is>
       </c>
-      <c r="B45" s="32" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>Revestimento externo com textura grafiato.</t>
         </is>
       </c>
-      <c r="C45" s="32" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="inlineStr">
+      <c r="A46" s="28" t="inlineStr">
         <is>
           <t>Prazo</t>
         </is>
       </c>
-      <c r="B46" s="32" t="inlineStr">
+      <c r="B46" s="28" t="inlineStr">
         <is>
           <t>Custos consideram prazo de obra de 41 meses;</t>
         </is>
       </c>
-      <c r="C46" s="32" t="inlineStr">
+      <c r="C46" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="32" t="inlineStr">
+      <c r="A47" s="28" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B47" s="32" t="inlineStr">
+      <c r="B47" s="28" t="inlineStr">
         <is>
           <t>Perfuração de estaca hélice contínua de 50 e 60cm – profundidade media 30m;</t>
         </is>
       </c>
-      <c r="C47" s="32" t="inlineStr">
+      <c r="C47" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="32" t="inlineStr">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>Infraestrutura</t>
         </is>
       </c>
-      <c r="B48" s="32" t="inlineStr">
+      <c r="B48" s="28" t="inlineStr">
         <is>
           <t>Concreto fck 40 Mpa com consideração de 5% de perda;</t>
         </is>
       </c>
-      <c r="C48" s="32" t="inlineStr">
+      <c r="C48" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="32" t="inlineStr">
+      <c r="A49" s="28" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B49" s="32" t="inlineStr">
+      <c r="B49" s="28" t="inlineStr">
         <is>
           <t>Concreto fck de 40 Mpa e 35 Mpa em supraestrutura, com consideração de 5% de perda;</t>
         </is>
       </c>
-      <c r="C49" s="32" t="inlineStr">
+      <c r="C49" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="inlineStr">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>Louças e Metais</t>
         </is>
       </c>
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B50" s="28" t="inlineStr">
         <is>
           <t>Consideração de entrega de vaso sanitário e acabamentos de registro em áreas privativas;</t>
         </is>
       </c>
-      <c r="C50" s="32" t="inlineStr">
+      <c r="C50" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="32" t="inlineStr">
+      <c r="A51" s="28" t="inlineStr">
         <is>
           <t>Louças e Metais</t>
         </is>
       </c>
-      <c r="B51" s="32" t="inlineStr">
+      <c r="B51" s="28" t="inlineStr">
         <is>
           <t>Considerado monocomando nos chuveiros</t>
         </is>
       </c>
-      <c r="C51" s="32" t="inlineStr">
+      <c r="C51" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
@@ -8130,7 +7798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8205,22 +7873,22 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Serviços de Brocas, Estacas Mega e Complementos</t>
+          <t>Mão de obra para execução de concreto armado em infraestrutura</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>40.43</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>150000</v>
+        <v>1173.42</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>150000</v>
+        <v>47441.3706</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
@@ -8237,91 +7905,27 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra para execução de concreto armado em infraestrutura</t>
+          <t>Lastro de concreto magro, aplicado em elementos de fundação, espessura 5 cm</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>40.43</v>
+        <v>120.06</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>1173.42</v>
+        <v>22.7471</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>47441.3706</v>
+        <v>2731.016826</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>somauma-virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Reforço de Infraestrutura e Taxa para Aprovação de Ligações de Água, Esgoto e Gás</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>somauma-virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Lastro de concreto magro, aplicado em elementos de fundação, espessura 5 cm</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>120.06</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>22.7471</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>2731.016826</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>somauma-virginia</t>
         </is>
@@ -9004,7 +8608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9111,22 +8715,22 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Consultoria Técnica e Revisão de Projeto de Drywall e Sistemas de Vedação</t>
+          <t>Mão de obra para execução de alvenaria estrutural</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>843.915</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>50000</v>
+        <v>46.92</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>50000</v>
+        <v>39596.4918</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
@@ -9143,7 +8747,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra para execução de alvenaria estrutural</t>
+          <t>Mão de obra para instalação de paredes com placa drywall</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -9152,13 +8756,13 @@
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>843.915</v>
+        <v>516.95</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>46.92</v>
+        <v>40</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>39596.4918</v>
+        <v>20678</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -9175,22 +8779,22 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra para instalação de paredes com placa drywall</t>
+          <t>Graute para alvenaria estrutural - fgk 20MPa</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>516.95</v>
+        <v>24.84</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>40</v>
+        <v>504</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>20678</v>
+        <v>12519.36</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
@@ -9207,22 +8811,22 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Graute para alvenaria estrutural - fgk 20MPa</t>
+          <t>Parede com sistema de chapas de Drywall duplo 70mm, placa standart e resistente à umidade (U/70/S)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>24.84</v>
+        <v>32.045</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>504</v>
+        <v>174.60065</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>12519.36</v>
+        <v>5595.07782925</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
@@ -9239,22 +8843,22 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Parede com sistema de chapas de Drywall duplo 70mm, placa standart e resistente à umidade (U/70/S)</t>
+          <t>Verga/Contraverga de Concreto moldada in loco</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>32.045</v>
+        <v>108.98</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>174.60065</v>
+        <v>59.3732</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>5595.07782925</v>
+        <v>6470.491336</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
@@ -9271,22 +8875,22 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Verga/Contraverga de Concreto moldada in loco</t>
+          <t>Parede com sistema de chapas de Drywall 48mm, com Isolamento Acústico, placa dupla standart (48/2S)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>108.98</v>
+        <v>30.185</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>59.3732</v>
+        <v>189.0573</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>6470.491336</v>
+        <v>5706.6946005</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -9303,7 +8907,7 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Parede com sistema de chapas de Drywall 48mm, com Isolamento Acústico, placa dupla standart (48/2S)</t>
+          <t>Parede com sistema de chapas de Drywall 70mm, placa standart (70/S)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -9312,13 +8916,13 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>30.185</v>
+        <v>51.69</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>189.0573</v>
+        <v>90.0782</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>5706.6946005</v>
+        <v>4656.142158</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
@@ -9335,7 +8939,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Parede com sistema de chapas de Drywall 70mm, placa standart (70/S)</t>
+          <t>Alvenaria de vedação de blocos cerâmicos furados na horizontal de 11,5x19x29 cm (espessura 11,5cm) com argamassa industrializada de assentamento</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -9344,13 +8948,13 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>51.69</v>
+        <v>40.96</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>90.0782</v>
+        <v>49.2492</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>4656.142158</v>
+        <v>2017.247232</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
@@ -9367,22 +8971,22 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Alvenaria de vedação de blocos cerâmicos furados na horizontal de 11,5x19x29 cm (espessura 11,5cm) com argamassa industrializada de assentamento</t>
+          <t>Encunhamento com Expansor</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>40.96</v>
+        <v>84.91</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>49.2492</v>
+        <v>15.82</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>2017.247232</v>
+        <v>1343.2762</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
@@ -9399,22 +9003,22 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Encunhamento com Expansor</t>
+          <t>Tela soldada para ligacao alvenaria/estrutura - para blocos de 9 a 14cm</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>84.91</v>
+        <v>105</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>15.82</v>
+        <v>2.99</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>1343.2762</v>
+        <v>313.95</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
@@ -9431,59 +9035,27 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Tela soldada para ligacao alvenaria/estrutura - para blocos de 9 a 14cm</t>
+          <t>Parede com sistema de chapas de Drywall 48mm, placa standart (48/S)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>105</v>
+        <v>1.1</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>2.99</v>
+        <v>73.31950000000001</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>313.95</v>
+        <v>80.65145000000001</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>somauma-virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>Parede com sistema de chapas de Drywall 48mm, placa standart (48/S)</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>73.31950000000001</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>80.65145000000001</v>
-      </c>
-      <c r="G17" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>somauma-virginia</t>
         </is>
@@ -9505,7 +9077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9772,22 +9344,22 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Consultoria Técnica em Impermeabilização</t>
+          <t>Mão de obra impermeabilização de reservatório</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>1</v>
+        <v>82.87</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>5000</v>
+        <v>36</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>5000</v>
+        <v>2983.32</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -9804,7 +9376,7 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra impermeabilização de reservatório</t>
+          <t>Mão de obra para impermeabilização de peitoris</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -9813,13 +9385,13 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>82.87</v>
+        <v>43.88</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>2983.32</v>
+        <v>1404.16</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
@@ -9836,7 +9408,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra para impermeabilização de peitoris</t>
+          <t>Impermeabilização de peitoris</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -9848,10 +9420,10 @@
         <v>43.88</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>32</v>
+        <v>25.5</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>1404.16</v>
+        <v>1118.94</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
@@ -9868,7 +9440,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Impermeabilização de peitoris</t>
+          <t>Mão de obra para impermeabilização de poço de elevador com cristalizante</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -9877,13 +9449,13 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43.88</v>
+        <v>51.4</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>25.5</v>
+        <v>15</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>1118.94</v>
+        <v>771</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
@@ -9900,7 +9472,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra para impermeabilização de poço de elevador com cristalizante</t>
+          <t>Impermeabilização em poço de elevador (Local II)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -9912,47 +9484,15 @@
         <v>51.4</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>15</v>
+        <v>10.8635</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>771</v>
+        <v>558.3839</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>somauma-virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>Impermeabilização em poço de elevador (Local II)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>10.8635</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>558.3839</v>
-      </c>
-      <c r="G16" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>somauma-virginia</t>
         </is>
@@ -10049,29 +9589,29 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra de instalações elétricas</t>
+          <t>Quadro distrib. chapa pintada - embutir</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>657047.95</v>
+        <v>2210</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>657047.95</v>
+        <v>247520</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -10081,29 +9621,29 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra de instalações hidráulicas</t>
+          <t>Interruptor DR 25A, 30mA, Tipo AC, bipolar</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>606505.8</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>606505.8</v>
+        <v>1228.64</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10113,29 +9653,29 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Quadros elétricos e disjuntores</t>
+          <t>Eletroduto PVC flexível - Eletroduto leve - 3/4"</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>1</v>
+        <v>23784.7</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>364721</v>
+        <v>3.375</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>364721</v>
+        <v>80273.3625</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -10145,29 +9685,29 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Fios e cabos elétricos</t>
+          <t>HIDRÔMETROS MULTIJATO CLASSE B DN25 (1") QN: 2,50 M³/H</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>281653.46</v>
+        <v>863.2</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>281653.46</v>
+        <v>97541.60000000001</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10177,29 +9717,29 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra de instalações preventivas</t>
+          <t>Eletroduto PVC flexível - Eletroduto pesado - 1.1/4"</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>8052</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>252710.75</v>
+        <v>9.1</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>252710.75</v>
+        <v>73273.2</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -10209,29 +9749,29 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Quadro distrib. chapa pintada - embutir</t>
+          <t>DPS Classe 2 275V/20kA Tripolar</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>2210</v>
+        <v>400.8</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>247520</v>
+        <v>400.8</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10241,7 +9781,7 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Interruptor DR 25A, 30mA, Tipo AC, bipolar</t>
+          <t>Quadro de distribuição, 500x1000x120mm</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -10250,13 +9790,13 @@
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>87.76000000000001</v>
+        <v>730.3099999999999</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>1228.64</v>
+        <v>79603.78999999999</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -10273,29 +9813,29 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Hidrantes e sprinklers</t>
+          <t>TUBO PVC ESG SN DN100</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>1</v>
+        <v>4289.45</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>114710.34</v>
+        <v>14.15</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>114710.34</v>
+        <v>60695.7175</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10305,7 +9845,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Eletroduto PVC flexível - Eletroduto leve - 3/4"</t>
+          <t>TUBO CPVC DN28</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -10314,20 +9854,20 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>23784.7</v>
+        <v>1396.1</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>3.375</v>
+        <v>40.9</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>80273.3625</v>
+        <v>57100.48999999999</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10337,29 +9877,29 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Sistema de bombas preventivas</t>
+          <t>Caixa de Luz 4''x4'', de embutir, em PVC para eletroduto corrugado</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>101747.4</v>
+        <v>1418.66</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>101747.4</v>
+        <v>65258.36</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10369,29 +9909,29 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Aprovação e legalização elétrico</t>
+          <t>TUBO PVC SOLD DN 25</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>1</v>
+        <v>20157.9</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>100000</v>
+        <v>2.75</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>100000</v>
+        <v>55434.22500000001</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10401,7 +9941,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>HIDRÔMETROS MULTIJATO CLASSE B DN25 (1") QN: 2,50 M³/H</t>
+          <t>Disjuntor Caixa Moldada Tripolar 90A, Curva C, 250/440V 6kA</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -10410,13 +9950,13 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>863.2</v>
+        <v>306.89</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>97541.60000000001</v>
+        <v>306.89</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
@@ -10433,7 +9973,7 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Eletroduto PVC flexível - Eletroduto pesado - 1.1/4"</t>
+          <t>TUBO CPVC DN22</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -10442,20 +9982,20 @@
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>8052</v>
+        <v>2111.3</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>9.1</v>
+        <v>24.39</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>73273.2</v>
+        <v>51494.607</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10465,22 +10005,22 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>DPS Classe 2 275V/20kA Tripolar</t>
+          <t>Mão de obra instalações SPDA</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>Unid.</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>1</v>
+        <v>14491.98</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>400.8</v>
+        <v>4</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>400.8</v>
+        <v>57967.92</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
@@ -10497,7 +10037,7 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Quadro de distribuição, 500x1000x120mm</t>
+          <t>Caixa de Passagem de sobrepor, 500x500x400mm, fabricado em PVC antichamas</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -10506,13 +10046,13 @@
         </is>
       </c>
       <c r="D19" s="25" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>730.3099999999999</v>
+        <v>921.96</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>79603.78999999999</v>
+        <v>52551.72</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
@@ -10529,22 +10069,22 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>TUBO PVC ESG SN DN100</t>
+          <t>MISTURADOR MONOCOMANDO Ø3/4"</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>4289.45</v>
+        <v>206</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>14.15</v>
+        <v>239.9</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>60695.7175</v>
+        <v>49419.4</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
@@ -10561,29 +10101,30 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>TUBO CPVC DN28</t>
+          <t>Disjuntor Tripolar Termomagnético -
+norma DIN (Curva C) - 125 A - 10 kA</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D21" s="25" t="n">
-        <v>1396.1</v>
+        <v>27</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>40.9</v>
+        <v>1534.495</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>57100.48999999999</v>
+        <v>41431.365</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -10593,22 +10134,22 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Caixa de Luz 4''x4'', de embutir, em PVC para eletroduto corrugado</t>
+          <t>Barramento Blindado BWW01-MA250J-54</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D22" s="25" t="n">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>1418.66</v>
+        <v>320</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>65258.36</v>
+        <v>45440</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
@@ -10625,22 +10166,22 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>TUBO PVC SOLD DN 25</t>
+          <t>Quadro de destribuição varíavel</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D23" s="25" t="n">
-        <v>20157.9</v>
+        <v>76</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>2.75</v>
+        <v>486.87</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>55434.22500000001</v>
+        <v>37002.12</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
@@ -10657,22 +10198,22 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Disjuntor Caixa Moldada Tripolar 90A, Curva C, 250/440V 6kA</t>
+          <t>TUBO PVC ESG SR DN100</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D24" s="25" t="n">
-        <v>1</v>
+        <v>1083.88</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>306.89</v>
+        <v>28.39</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>306.89</v>
+        <v>30771.35320000001</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>1</v>
@@ -10689,22 +10230,22 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>TUBO CPVC DN22</t>
+          <t>Mini Disjuntor Monopolar 16A, Curva C, 250/440V 3kA</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>2111.3</v>
+        <v>15</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>24.39</v>
+        <v>11.4</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>51494.607</v>
+        <v>171</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
@@ -10721,22 +10262,22 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra instalações SPDA</t>
+          <t>Mini Disjuntor Monopolar 10A, Curva C, 250/440V 3kA</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>Unid.</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>14491.98</v>
+        <v>21</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>4</v>
+        <v>7.91</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>57967.92</v>
+        <v>166.11</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>1</v>
@@ -10753,29 +10294,30 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Caixa de Passagem de sobrepor, 500x500x400mm, fabricado em PVC antichamas</t>
+          <t>Interruptor bipolar DR (fase/neutro - In
+30mA) - DIN - 40 A</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>57</v>
+        <v>186</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>921.96</v>
+        <v>168.99</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>52551.72</v>
+        <v>31432.14</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -10785,29 +10327,29 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra de telecomunicações</t>
+          <t>REGISTRO DE GAVETA Ø3/4"</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>1</v>
+        <v>867</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>50542.15</v>
+        <v>31.72</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>50542.15</v>
+        <v>27501.24</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10817,29 +10359,29 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Consultoria Técnica e Análise e Revisão de Projetos para Instalações Elétricas e Hidraúlicas</t>
+          <t>Interruptor tetrapolar DR (3 fases/neutro - In 30mA) - DIN - 63 A</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>50000</v>
+        <v>252.89</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>50000</v>
+        <v>25794.78</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10391,7 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>MISTURADOR MONOCOMANDO Ø3/4"</t>
+          <t>S/ placa - Tomada hexagonal (NBR 14136) 2P+T 10A</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -10858,20 +10400,20 @@
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>206</v>
+        <v>3059</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>239.9</v>
+        <v>7.9</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>49419.4</v>
+        <v>24166.1</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -10881,30 +10423,29 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Disjuntor Tripolar Termomagnético -
-norma DIN (Curva C) - 125 A - 10 kA</t>
+          <t>CONECT TRANS FM SUPER CPVC DN22X1/2 CB</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>27</v>
+        <v>1268</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>1534.495</v>
+        <v>19.04</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>41431.365</v>
+        <v>24142.72</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10455,7 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Barramento Blindado BWW01-MA250J-54</t>
+          <t>TUBO PVC ESG SN DN50</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -10923,13 +10464,13 @@
         </is>
       </c>
       <c r="D32" s="25" t="n">
-        <v>142</v>
+        <v>2156.2</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>320</v>
+        <v>9.65</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>45440</v>
+        <v>20807.33</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>1</v>
@@ -10946,7 +10487,7 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Quadro de destribuição varíavel</t>
+          <t>Conjunto motobombas de recalque - 6,97m³/h 95,73 mca 4cv</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -10955,13 +10496,13 @@
         </is>
       </c>
       <c r="D33" s="25" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>486.87</v>
+        <v>5809.85</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>37002.12</v>
+        <v>23239.4</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>1</v>
@@ -10978,7 +10519,7 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>TUBO PVC ESG SR DN100</t>
+          <t>Tubo de Aço Galvanizado - Ø65</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -10987,20 +10528,20 @@
         </is>
       </c>
       <c r="D34" s="25" t="n">
-        <v>1083.88</v>
+        <v>203.92</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>28.39</v>
+        <v>107.3</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>30771.35320000001</v>
+        <v>21880.616</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11095,29 +10636,29 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Elevadores</t>
+          <t>PISCINA ADULTA 1</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>1.1999999999999993</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>61.92</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>1172000</v>
+        <v>74.30399999999996</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>1172000</v>
+        <v>4600.903679999998</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11127,29 +10668,29 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Grupo gerador</t>
+          <t>SDAI - Acionador manual + avisador audio visual de alarme</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>99400</v>
+        <v>201.98</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>99400</v>
+        <v>7473.26</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -11159,22 +10700,22 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Sistema de CFTV</t>
+          <t>Pintura com tinta látex PVA em poços dos elevadores, 2 demãos</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>1</v>
+        <v>1594.49</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>92243</v>
+        <v>4.6135</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>92243</v>
+        <v>7356.179615</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -11191,29 +10732,29 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>PISCINA ADULTA 1</t>
+          <t>Revestimento de granito em piso do elevador</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>1.1999999999999993</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>61.92</v>
+        <v>12.35</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>74.30399999999996</v>
+        <v>556.755</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>4600.903679999998</v>
+        <v>6875.92425</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>somauma-virginia</t>
         </is>
       </c>
     </row>
@@ -11223,29 +10764,29 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>KIT FP-6-2-SI FONTE INTERATIVA COM 6 JATOS</t>
+          <t>Gerador de Cloro à base sal com capacidade de gerar 20g de cloro puro por hora</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>35200</v>
+        <v>4170</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>35200</v>
+        <v>6255</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>xpcon-porto-cerro</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -11255,29 +10796,29 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>trocador de Calor TIV Para Piscinas - Sodramar (Full Inverter) tiv-45</t>
+          <t>PISCINA INFANTIL</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>0.6500000000000004</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>1</v>
+        <v>7.62</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>16200</v>
+        <v>4.953000000000003</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>16200</v>
+        <v>37.74186000000002</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>xpcon-porto-cerro</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11287,29 +10828,29 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra para instalação</t>
+          <t>GERADOR DE COLORO BZ -20</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>10304.38666666667</v>
+        <v>3296.12</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>10304.38666666667</v>
+        <v>4944.18</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby, viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11319,29 +10860,29 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Central de Alarmes</t>
+          <t>MOTOBOMBA SYLLENT AUTO ESCORVANTE 1/3CV Mono</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>7660.4</v>
+        <v>1166</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>7660.4</v>
+        <v>4664</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>cln-porto-ruby</t>
         </is>
       </c>
     </row>
@@ -11351,7 +10892,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>SDAI - Acionador manual + avisador audio visual de alarme</t>
+          <t>GERADOR DE COLORO BZ -30</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -11360,20 +10901,20 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>201.98</v>
+        <v>3656.75</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>7473.26</v>
+        <v>3656.75</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby, viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11383,29 +10924,29 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>GERADOR DE CLORO SODRAMAR MOD.GS 42-220V</t>
+          <t>MOTOBOMBA SYLLENT AUTO ESCORVANTE 3/4CV Mono</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>7409</v>
+        <v>1699</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>7409</v>
+        <v>3398</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>xpcon-porto-cerro</t>
+          <t>cln-porto-ruby</t>
         </is>
       </c>
     </row>
@@ -11415,29 +10956,29 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Pintura com tinta látex PVA em poços dos elevadores, 2 demãos</t>
+          <t>TAMPA ARTICULADA GDA 110X110cm CÓDIGO 3140</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>1594.49</v>
+        <v>1</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>4.6135</v>
+        <v>3200</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>7356.179615</v>
+        <v>3200</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>cln-porto-ruby, viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11447,29 +10988,29 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Revestimento de granito em piso do elevador</t>
+          <t>Refletor em LED 20W RGB c/ ângulo 150º, encaixe em tubo de 25mm com vedação total d’água em Viton, em aço inox 316 (Inox Puro), com lente em policarbonato</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>12.35</v>
+        <v>7</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>556.755</v>
+        <v>426</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>6875.92425</v>
+        <v>2982</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11020,7 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Gerador de Cloro à base sal com capacidade de gerar 20g de cloro puro por hora</t>
+          <t>TAMPA GDA REBAIXADA C/ GRELHA 80X80cm CÓDIGO 3078</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -11491,17 +11032,17 @@
         <v>1.5</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>4170</v>
+        <v>1850</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>6255</v>
+        <v>2775</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby, viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11511,29 +11052,29 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Gerador de Energia Emergêncial</t>
+          <t>SDAI - Repetidora de central de alarme endereçavel</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>6000</v>
+        <v>1048.76</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>6000</v>
+        <v>2097.52</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -11543,29 +11084,29 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>PISCINA INFANTIL</t>
+          <t>SDAI - Central de alarme endereçavel</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>0.6500000000000004</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D19" s="25" t="n">
-        <v>7.62</v>
+        <v>1</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>4.953000000000003</v>
+        <v>2068.81</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>37.74186000000002</v>
+        <v>2068.81</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11116,8 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>GERADOR DE COLORO BZ -20</t>
+          <t>Bomba 3/4 cv BM-75 p/ piscinas de até 78 mil litros
+SODAMAR</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -11584,20 +11126,20 @@
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>3296.12</v>
+        <v>1603</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>4944.18</v>
+        <v>1603</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby, viva4-barra4</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11607,7 +11149,8 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>MOTOBOMBA SYLLENT AUTO ESCORVANTE 1/3CV Mono</t>
+          <t>Filtro para piscina FM-50 p/ até 78 mil litros
+SODAMAR</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -11616,20 +11159,20 @@
         </is>
       </c>
       <c r="D21" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>1166</v>
+        <v>1443</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>4664</v>
+        <v>1443</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11639,22 +11182,22 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Material hidráulico e elétrico</t>
+          <t>MOTOBOMBA SODRAMAR BMP-25</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D22" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>4121.754666666668</v>
+        <v>716</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>4121.754666666668</v>
+        <v>1432</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
@@ -11671,29 +11214,29 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Sistema de alarme perimetal</t>
+          <t>FILTRO SODRAMAR FM-36 – COM 40kg areia</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D23" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>3931</v>
+        <v>714</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>3931</v>
+        <v>1428</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>somauma-virginia</t>
+          <t>cln-porto-ruby</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11246,7 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>GERADOR DE COLORO BZ -30</t>
+          <t>Coadeira modelo Padrão – Sodramar</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -11712,20 +11255,20 @@
         </is>
       </c>
       <c r="D24" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>3656.75</v>
+        <v>785</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>3656.75</v>
+        <v>1177.5</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby, viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11278,7 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>MOTOBOMBA SYLLENT AUTO ESCORVANTE 3/4CV Mono</t>
+          <t>FILTRO SODRAMAR FM-50 – COM 125kg areia</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -11744,13 +11287,13 @@
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>1699</v>
+        <v>1162</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>3398</v>
+        <v>1162</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
@@ -11767,7 +11310,7 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>TAMPA ARTICULADA GDA 110X110cm CÓDIGO 3140</t>
+          <t>FILTRO DE PISCINA SODRAMAR FM-30</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -11776,20 +11319,20 @@
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>3200</v>
+        <v>580</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>3200</v>
+        <v>1160</v>
       </c>
       <c r="G26" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby, viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -11799,7 +11342,7 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Refletor em LED 20W RGB c/ ângulo 150º, encaixe em tubo de 25mm com vedação total d’água em Viton, em aço inox 316 (Inox Puro), com lente em policarbonato</t>
+          <t>Comando para LED com troca de cores, Controle Remoto</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -11808,13 +11351,13 @@
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>426</v>
+        <v>720</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>2982</v>
+        <v>1080</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>1</v>
@@ -11831,7 +11374,8 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>TAMPA GDA REBAIXADA C/ GRELHA 80X80cm CÓDIGO 3078</t>
+          <t>Bomba 1/4 cv BM-25 p/ piscinas de até 28 mil litros
+SODAMAR</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -11840,20 +11384,20 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>1850</v>
+        <v>1055</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>2775</v>
+        <v>1055</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby, viva4-barra4</t>
+          <t>viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11863,29 +11407,29 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>SDAI - Repetidora de central de alarme endereçavel</t>
+          <t>GRADE DE FUNDO 15cm X 15cm COM TAMPA FSB BASE LATÃO</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D29" s="25" t="n">
         <v>2</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>1048.76</v>
+        <v>505.09</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>2097.52</v>
+        <v>1010.18</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>xpcon-porto-cerro</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11439,7 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>SDAI - Central de alarme endereçavel</t>
+          <t>COADEIRA COMPACTA CRISTAL LED EM ABS C/ ACABAMENTO FRENTE EM INOX</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -11907,17 +11451,17 @@
         <v>1</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>2068.81</v>
+        <v>889</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>2068.81</v>
+        <v>889</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="24" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>cln-porto-ruby, viva4-barra4</t>
         </is>
       </c>
     </row>
@@ -11927,8 +11471,7 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Bomba 3/4 cv BM-75 p/ piscinas de até 78 mil litros
-SODAMAR</t>
+          <t>FILTRO DE PISCINA SODRAMAR FM-40</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -11940,17 +11483,17 @@
         <v>1</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>1603</v>
+        <v>838</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>1603</v>
+        <v>838</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
@@ -11960,30 +11503,29 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Filtro para piscina FM-50 p/ até 78 mil litros
-SODAMAR</t>
+          <t>CAIXA PARA QUADRO DE COMANDO - IP 66</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1443</v>
+        <v>833.54</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>1443</v>
+        <v>833.54</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="24" t="inlineStr">
         <is>
-          <t>viva4-barra4</t>
+          <t>xpcon-porto-cerro</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11535,7 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>MOTOBOMBA SODRAMAR BMP-25</t>
+          <t>MOTOBOMBA SODRAMAR BMP-50</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -12002,13 +11544,13 @@
         </is>
       </c>
       <c r="D33" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>716</v>
+        <v>831</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>1432</v>
+        <v>831</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>1</v>
@@ -12025,29 +11567,29 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>FILTRO SODRAMAR FM-36 – COM 40kg areia</t>
+          <t>ELETROBOMBA SODRAMAR BMC-33 (1/3 VC)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>714</v>
+        <v>805</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>1428</v>
+        <v>805</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="24" t="inlineStr">
         <is>
-          <t>cln-porto-ruby</t>
+          <t>xpcon-porto-cerro</t>
         </is>
       </c>
     </row>
